--- a/data_transportation_faculty.xlsx
+++ b/data_transportation_faculty.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\appuals\Documents\Demographics Paper Part 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\appuals\Documents\Demographics Paper Part 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83C2991-322C-48DF-9ABF-9E3AD5394C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1443B40-DD87-4043-8607-80E60AC3342A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17790" yWindow="2160" windowWidth="19050" windowHeight="11445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="University Rankings" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="512">
   <si>
     <t>School</t>
   </si>
@@ -921,9 +921,6 @@
     <t>Shandong University</t>
   </si>
   <si>
-    <t>Missisippi State University</t>
-  </si>
-  <si>
     <t>Universitat Politècnica de València (UPV)</t>
   </si>
   <si>
@@ -1020,9 +1017,6 @@
     <t>Bucknell University</t>
   </si>
   <si>
-    <t>Illinois Institue of Technology</t>
-  </si>
-  <si>
     <t>Xi’an Jiaotong University</t>
   </si>
   <si>
@@ -1128,9 +1122,6 @@
     <t>Pakistan</t>
   </si>
   <si>
-    <t>City College of New York</t>
-  </si>
-  <si>
     <t>National Taiwan University</t>
   </si>
   <si>
@@ -1275,9 +1266,6 @@
     <t>Wuhan University</t>
   </si>
   <si>
-    <t>University of Nebraska</t>
-  </si>
-  <si>
     <t>University of Patras</t>
   </si>
   <si>
@@ -1314,9 +1302,6 @@
     <t>Yonsei University</t>
   </si>
   <si>
-    <t>University of Alaska Fairbanks</t>
-  </si>
-  <si>
     <t>Al-Azhar University</t>
   </si>
   <si>
@@ -1369,9 +1354,6 @@
   </si>
   <si>
     <t>Beijing University of Aeronautics and Astronautics</t>
-  </si>
-  <si>
-    <t>University of Cincinati</t>
   </si>
   <si>
     <t>National University of San Juan</t>
@@ -1982,7 +1964,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>6</v>
@@ -1999,7 +1981,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>6</v>
@@ -2017,7 +1999,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>6</v>
@@ -2035,7 +2017,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>6</v>
@@ -2053,7 +2035,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
@@ -2071,7 +2053,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>13</v>
@@ -2088,7 +2070,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>6</v>
@@ -2105,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>13</v>
@@ -2122,7 +2104,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>6</v>
@@ -2139,7 +2121,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>13</v>
@@ -2156,7 +2138,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>13</v>
@@ -2173,7 +2155,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>6</v>
@@ -2190,7 +2172,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>13</v>
@@ -2207,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>13</v>
@@ -2224,7 +2206,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>6</v>
@@ -2241,7 +2223,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>6</v>
@@ -2258,7 +2240,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>13</v>
@@ -2276,7 +2258,7 @@
         <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>6</v>
@@ -2294,7 +2276,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>6</v>
@@ -2311,7 +2293,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>6</v>
@@ -2328,7 +2310,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>6</v>
@@ -2345,7 +2327,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>6</v>
@@ -2362,7 +2344,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>13</v>
@@ -2379,7 +2361,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>6</v>
@@ -2396,7 +2378,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>6</v>
@@ -2413,7 +2395,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>13</v>
@@ -2430,7 +2412,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>13</v>
@@ -2447,7 +2429,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>6</v>
@@ -2464,7 +2446,7 @@
         <v>28</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>13</v>
@@ -2479,7 +2461,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>6</v>
@@ -2496,7 +2478,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>6</v>
@@ -2513,7 +2495,7 @@
         <v>31</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>13</v>
@@ -2530,7 +2512,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>6</v>
@@ -2541,13 +2523,13 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1">
       <c r="A35" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B35" s="5">
         <v>33</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>6</v>
@@ -2564,7 +2546,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>6</v>
@@ -2581,7 +2563,7 @@
         <v>33</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>13</v>
@@ -2596,7 +2578,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>13</v>
@@ -2613,7 +2595,7 @@
         <v>37</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>13</v>
@@ -2628,7 +2610,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>6</v>
@@ -2645,7 +2627,7 @@
         <v>37</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>6</v>
@@ -2662,7 +2644,7 @@
         <v>37</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>6</v>
@@ -2677,7 +2659,7 @@
         <v>37</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>13</v>
@@ -2692,7 +2674,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>6</v>
@@ -2707,7 +2689,7 @@
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>6</v>
@@ -2722,7 +2704,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>6</v>
@@ -2739,7 +2721,7 @@
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>6</v>
@@ -2754,7 +2736,7 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>6</v>
@@ -2771,7 +2753,7 @@
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>6</v>
@@ -2788,7 +2770,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>6</v>
@@ -2805,7 +2787,7 @@
         <v>49</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>6</v>
@@ -2822,7 +2804,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>6</v>
@@ -2837,7 +2819,7 @@
         <v>51</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>13</v>
@@ -2852,7 +2834,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>6</v>
@@ -2867,7 +2849,7 @@
         <v>51</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>6</v>
@@ -2882,7 +2864,7 @@
         <v>51</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>13</v>
@@ -2897,7 +2879,7 @@
         <v>51</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>6</v>
@@ -2912,7 +2894,7 @@
         <v>51</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>6</v>
@@ -2927,7 +2909,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>13</v>
@@ -2942,7 +2924,7 @@
         <v>58</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>13</v>
@@ -2959,7 +2941,7 @@
         <v>58</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>6</v>
@@ -2974,7 +2956,7 @@
         <v>58</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>6</v>
@@ -2989,7 +2971,7 @@
         <v>58</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>6</v>
@@ -3004,7 +2986,7 @@
         <v>58</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>6</v>
@@ -3019,7 +3001,7 @@
         <v>58</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>6</v>
@@ -3034,7 +3016,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>6</v>
@@ -3049,7 +3031,7 @@
         <v>65</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>6</v>
@@ -3064,7 +3046,7 @@
         <v>65</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>6</v>
@@ -3079,7 +3061,7 @@
         <v>65</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>6</v>
@@ -3094,7 +3076,7 @@
         <v>65</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>6</v>
@@ -3111,7 +3093,7 @@
         <v>65</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>6</v>
@@ -3126,7 +3108,7 @@
         <v>65</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>6</v>
@@ -3141,7 +3123,7 @@
         <v>65</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>6</v>
@@ -3156,7 +3138,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>6</v>
@@ -3171,7 +3153,7 @@
         <v>73</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>6</v>
@@ -3186,7 +3168,7 @@
         <v>73</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>6</v>
@@ -3201,7 +3183,7 @@
         <v>73</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>6</v>
@@ -3218,7 +3200,7 @@
         <v>73</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>6</v>
@@ -3233,7 +3215,7 @@
         <v>73</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>6</v>
@@ -3248,7 +3230,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>6</v>
@@ -3263,7 +3245,7 @@
         <v>79</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>13</v>
@@ -3278,7 +3260,7 @@
         <v>79</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>6</v>
@@ -3293,7 +3275,7 @@
         <v>79</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>13</v>
@@ -3308,7 +3290,7 @@
         <v>79</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>6</v>
@@ -3323,7 +3305,7 @@
         <v>79</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>6</v>
@@ -3338,7 +3320,7 @@
         <v>79</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>6</v>
@@ -3353,7 +3335,7 @@
         <v>79</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>6</v>
@@ -3368,7 +3350,7 @@
         <v>79</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>6</v>
@@ -3383,7 +3365,7 @@
         <v>79</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>6</v>
@@ -3398,7 +3380,7 @@
         <v>79</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>6</v>
@@ -3413,7 +3395,7 @@
         <v>79</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>13</v>
@@ -3428,7 +3410,7 @@
         <v>91</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>13</v>
@@ -3443,7 +3425,7 @@
         <v>91</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>13</v>
@@ -3458,7 +3440,7 @@
         <v>91</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>6</v>
@@ -3473,7 +3455,7 @@
         <v>91</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>6</v>
@@ -3488,7 +3470,7 @@
         <v>91</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>6</v>
@@ -3503,7 +3485,7 @@
         <v>91</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>6</v>
@@ -3518,7 +3500,7 @@
         <v>91</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>6</v>
@@ -3533,7 +3515,7 @@
         <v>91</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>6</v>
@@ -3548,7 +3530,7 @@
         <v>91</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>6</v>
@@ -3563,7 +3545,7 @@
         <v>91</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>6</v>
@@ -3578,7 +3560,7 @@
         <v>91</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>6</v>
@@ -3593,7 +3575,7 @@
         <v>91</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>6</v>
@@ -3608,7 +3590,7 @@
         <v>91</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>6</v>
@@ -3623,7 +3605,7 @@
         <v>91</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>6</v>
@@ -3638,7 +3620,7 @@
         <v>91</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>6</v>
@@ -3653,7 +3635,7 @@
         <v>91</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>13</v>
@@ -8615,7 +8597,7 @@
         <v>32</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>294</v>
+        <v>126</v>
       </c>
       <c r="C108" s="2" t="str">
         <f t="shared" si="1"/>
@@ -8751,13 +8733,13 @@
         <v>192</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>214</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>214</v>
@@ -8781,16 +8763,16 @@
         <v>188</v>
       </c>
       <c r="E113" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F113" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F113" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="G113" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="I113" s="2">
         <v>2021</v>
@@ -8815,7 +8797,7 @@
         <v>179</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>182</v>
@@ -8924,7 +8906,7 @@
         <v>2018</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>221</v>
@@ -9071,7 +9053,7 @@
         <v>192</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>200</v>
@@ -9167,7 +9149,7 @@
         <v>188</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>187</v>
@@ -9261,7 +9243,7 @@
         <v>188</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>196</v>
@@ -9295,13 +9277,13 @@
         <v>192</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>207</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>182</v>
@@ -9464,7 +9446,7 @@
         <v>289</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>27</v>
@@ -9499,7 +9481,7 @@
         <v>182</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>182</v>
@@ -9615,7 +9597,7 @@
         <v>188</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>187</v>
@@ -9793,7 +9775,7 @@
         <v>188</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>209</v>
@@ -9808,7 +9790,7 @@
         <v>2021</v>
       </c>
       <c r="J145" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K145" s="2" t="s">
         <v>266</v>
@@ -9955,7 +9937,7 @@
         <v>192</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>200</v>
@@ -9977,7 +9959,7 @@
         <v>46</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C151" s="2" t="str">
         <f t="shared" si="2"/>
@@ -10083,7 +10065,7 @@
         <v>192</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>182</v>
@@ -10183,7 +10165,7 @@
         <v>179</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>207</v>
@@ -10213,7 +10195,7 @@
         <v>179</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>181</v>
@@ -10264,7 +10246,7 @@
     </row>
     <row r="160" spans="1:11" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B160" s="2"/>
       <c r="C160" s="2" t="str">
@@ -10275,7 +10257,7 @@
         <v>192</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>190</v>
@@ -10294,7 +10276,7 @@
     </row>
     <row r="161" spans="1:11" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B161" s="2"/>
       <c r="C161" s="2" t="str">
@@ -10328,7 +10310,7 @@
     </row>
     <row r="162" spans="1:11" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B162" s="2"/>
       <c r="C162" s="2" t="str">
@@ -10339,10 +10321,10 @@
         <v>188</v>
       </c>
       <c r="E162" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>11</v>
@@ -10358,7 +10340,7 @@
     </row>
     <row r="163" spans="1:11" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>104</v>
@@ -10371,7 +10353,7 @@
         <v>179</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F163" s="2" t="s">
         <v>270</v>
@@ -10390,7 +10372,7 @@
     </row>
     <row r="164" spans="1:11" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>93</v>
@@ -10549,7 +10531,7 @@
         <v>50</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C169" s="2" t="str">
         <f t="shared" si="2"/>
@@ -10559,7 +10541,7 @@
         <v>179</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>196</v>
@@ -10589,7 +10571,7 @@
         <v>179</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>182</v>
@@ -10623,7 +10605,7 @@
         <v>179</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>211</v>
@@ -10681,7 +10663,7 @@
         <v>192</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>196</v>
@@ -10696,7 +10678,7 @@
         <v>2010</v>
       </c>
       <c r="J173" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K173" s="2" t="s">
         <v>292</v>
@@ -10707,7 +10689,7 @@
         <v>53</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C174" s="2" t="str">
         <f t="shared" si="2"/>
@@ -10717,10 +10699,10 @@
         <v>179</v>
       </c>
       <c r="E174" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="F174" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="G174" s="3" t="s">
         <v>10</v>
@@ -10775,7 +10757,7 @@
         <v>53</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C176" s="2" t="str">
         <f t="shared" si="2"/>
@@ -10807,7 +10789,7 @@
         <v>54</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>327</v>
+        <v>125</v>
       </c>
       <c r="C177" s="2" t="str">
         <f t="shared" si="2"/>
@@ -10817,7 +10799,7 @@
         <v>179</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>196</v>
@@ -10853,7 +10835,7 @@
         <v>179</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>190</v>
@@ -10943,7 +10925,7 @@
         <v>188</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>196</v>
@@ -10992,7 +10974,7 @@
         <v>2017</v>
       </c>
       <c r="J182" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="K182" s="2" t="s">
         <v>292</v>
@@ -11011,10 +10993,10 @@
         <v>179</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G183" s="2" t="s">
         <v>10</v>
@@ -11043,7 +11025,7 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>216</v>
@@ -11067,7 +11049,7 @@
         <v>179</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>187</v>
@@ -11221,10 +11203,10 @@
         <v>179</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>27</v>
@@ -11369,7 +11351,7 @@
         <v>192</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F195" s="2" t="s">
         <v>182</v>
@@ -11490,7 +11472,7 @@
         <v>179</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F199" s="2" t="s">
         <v>263</v>
@@ -11790,7 +11772,7 @@
         <v>61</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C209" s="2" t="str">
         <f t="shared" si="3"/>
@@ -11800,7 +11782,7 @@
         <v>179</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>270</v>
@@ -11832,7 +11814,7 @@
         <v>179</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>270</v>
@@ -11852,7 +11834,7 @@
         <v>61</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C211" s="2" t="str">
         <f t="shared" si="3"/>
@@ -11884,7 +11866,7 @@
         <v>61</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C212" s="2" t="str">
         <f t="shared" si="3"/>
@@ -12016,7 +11998,7 @@
         <v>179</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>200</v>
@@ -12082,16 +12064,16 @@
         <v>179</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I218" s="2">
         <v>1978</v>
@@ -12172,16 +12154,16 @@
         <v>188</v>
       </c>
       <c r="E221" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F221" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="G221" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H221" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="H221" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="I221" s="2">
         <v>2018</v>
@@ -12206,7 +12188,7 @@
         <v>188</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>187</v>
@@ -12242,10 +12224,10 @@
         <v>179</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G223" s="2" t="s">
         <v>24</v>
@@ -12424,7 +12406,7 @@
         <v>179</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>182</v>
@@ -12452,7 +12434,7 @@
         <v>179</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>182</v>
@@ -12482,7 +12464,7 @@
         <v>188</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>182</v>
@@ -12516,7 +12498,7 @@
         <v>188</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>200</v>
@@ -12617,7 +12599,7 @@
         <v>66</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C236" s="2" t="str">
         <f t="shared" si="3"/>
@@ -12729,7 +12711,7 @@
         <v>179</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F240" s="2" t="s">
         <v>196</v>
@@ -12757,7 +12739,7 @@
         <v>188</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>187</v>
@@ -12785,10 +12767,10 @@
         <v>179</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G242" s="2" t="s">
         <v>68</v>
@@ -12843,10 +12825,10 @@
         <v>188</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G244" s="2" t="s">
         <v>5</v>
@@ -12858,7 +12840,7 @@
         <v>2020</v>
       </c>
       <c r="J244" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K244" s="2" t="s">
         <v>292</v>
@@ -12869,7 +12851,7 @@
         <v>68</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C245" s="2" t="str">
         <f t="shared" si="3"/>
@@ -12918,7 +12900,7 @@
         <v>2009</v>
       </c>
       <c r="J246" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="K246" s="2" t="s">
         <v>292</v>
@@ -12937,7 +12919,7 @@
         <v>179</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F247" s="2" t="s">
         <v>207</v>
@@ -13001,7 +12983,7 @@
         <v>192</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>196</v>
@@ -13117,7 +13099,7 @@
         <v>71</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C253" s="2" t="str">
         <f t="shared" si="3"/>
@@ -13185,10 +13167,10 @@
         <v>179</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G255" s="2" t="s">
         <v>43</v>
@@ -13237,7 +13219,7 @@
         <v>72</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>363</v>
+        <v>122</v>
       </c>
       <c r="C257" s="2" t="str">
         <f t="shared" si="3"/>
@@ -13343,10 +13325,10 @@
         <v>179</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G260" s="2" t="s">
         <v>9</v>
@@ -13395,7 +13377,7 @@
         <v>72</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C262" s="2" t="str">
         <f t="shared" si="4"/>
@@ -13405,10 +13387,10 @@
         <v>179</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G262" s="2" t="s">
         <v>25</v>
@@ -13435,7 +13417,7 @@
         <v>188</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>196</v>
@@ -13450,7 +13432,7 @@
         <v>2020</v>
       </c>
       <c r="J263" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="K263" s="2" t="s">
         <v>292</v>
@@ -13471,7 +13453,7 @@
         <v>179</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F264" s="2" t="s">
         <v>182</v>
@@ -13493,7 +13475,7 @@
         <v>74</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C265" s="2" t="str">
         <f t="shared" si="4"/>
@@ -13569,7 +13551,7 @@
         <v>179</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F267" s="2" t="s">
         <v>200</v>
@@ -13689,10 +13671,10 @@
         <v>188</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G271" s="2" t="s">
         <v>11</v>
@@ -13723,7 +13705,7 @@
         <v>188</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>187</v>
@@ -13757,10 +13739,10 @@
         <v>188</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G273" s="2" t="s">
         <v>25</v>
@@ -13787,10 +13769,10 @@
         <v>179</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G274" s="2" t="s">
         <v>11</v>
@@ -13877,7 +13859,7 @@
         <v>188</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F277" s="2" t="s">
         <v>196</v>
@@ -13971,7 +13953,7 @@
         <v>188</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>207</v>
@@ -14007,7 +13989,7 @@
         <v>192</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F281" s="2" t="s">
         <v>187</v>
@@ -14072,7 +14054,7 @@
         <v>289</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G283" s="2" t="s">
         <v>10</v>
@@ -14149,7 +14131,7 @@
         <v>78</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C286" s="2" t="str">
         <f t="shared" si="4"/>
@@ -14159,10 +14141,10 @@
         <v>179</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G286" s="2" t="s">
         <v>79</v>
@@ -14257,10 +14239,10 @@
         <v>192</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G289" s="2" t="s">
         <v>55</v>
@@ -14433,7 +14415,7 @@
         <v>81</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C295" s="2" t="str">
         <f t="shared" si="4"/>
@@ -14465,7 +14447,7 @@
         <v>81</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C296" s="2" t="str">
         <f t="shared" si="4"/>
@@ -14475,7 +14457,7 @@
         <v>192</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>270</v>
@@ -14565,7 +14547,7 @@
         <v>188</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>196</v>
@@ -14635,13 +14617,13 @@
         <v>179</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>196</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>182</v>
@@ -14741,7 +14723,7 @@
         <v>83</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C305" s="2" t="str">
         <f t="shared" si="4"/>
@@ -14751,7 +14733,7 @@
         <v>192</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>207</v>
@@ -14834,7 +14816,7 @@
         <v>83</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C308" s="2" t="str">
         <f t="shared" si="4"/>
@@ -14844,10 +14826,10 @@
         <v>179</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G308" s="2" t="s">
         <v>21</v>
@@ -14887,10 +14869,10 @@
         <v>2013</v>
       </c>
       <c r="J309" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="K309" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="310" spans="1:11" ht="22.5" customHeight="1">
@@ -14940,13 +14922,13 @@
         <v>188</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F311" s="2" t="s">
         <v>196</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>235</v>
@@ -14974,10 +14956,10 @@
         <v>179</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G312" s="2" t="s">
         <v>264</v>
@@ -15023,7 +15005,7 @@
         <v>2002</v>
       </c>
       <c r="J313" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="K313" s="2" t="s">
         <v>182</v>
@@ -15034,7 +15016,7 @@
         <v>84</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C314" s="2" t="str">
         <f t="shared" si="4"/>
@@ -15055,7 +15037,7 @@
         <v>2001</v>
       </c>
       <c r="J314" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="K314" s="2" t="s">
         <v>235</v>
@@ -15104,7 +15086,7 @@
         <v>179</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F316" s="2" t="s">
         <v>190</v>
@@ -15170,7 +15152,7 @@
         <v>188</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F318" s="2" t="s">
         <v>196</v>
@@ -15202,10 +15184,10 @@
         <v>192</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G319" s="2" t="s">
         <v>50</v>
@@ -15232,7 +15214,7 @@
         <v>179</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F320" s="2" t="s">
         <v>196</v>
@@ -15262,7 +15244,7 @@
         <v>179</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F321" s="2" t="s">
         <v>196</v>
@@ -15358,7 +15340,7 @@
         <v>179</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F324" s="2" t="s">
         <v>182</v>
@@ -15388,7 +15370,7 @@
         <v>179</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F325" s="2" t="s">
         <v>200</v>
@@ -15418,7 +15400,7 @@
         <v>179</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F326" s="2" t="s">
         <v>207</v>
@@ -15506,7 +15488,7 @@
         <v>179</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F329" s="2" t="s">
         <v>200</v>
@@ -15540,7 +15522,7 @@
         <v>188</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F330" s="2" t="s">
         <v>270</v>
@@ -15574,7 +15556,7 @@
         <v>192</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F331" s="2" t="s">
         <v>196</v>
@@ -15608,7 +15590,7 @@
         <v>188</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F332" s="2" t="s">
         <v>263</v>
@@ -15676,10 +15658,10 @@
         <v>179</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G334" s="2" t="s">
         <v>29</v>
@@ -15740,7 +15722,7 @@
         <v>188</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F336" s="2" t="s">
         <v>187</v>
@@ -15774,7 +15756,7 @@
         <v>188</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F337" s="2" t="s">
         <v>207</v>
@@ -15866,7 +15848,7 @@
         <v>192</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="F340" s="2" t="s">
         <v>196</v>
@@ -15896,7 +15878,7 @@
         <v>179</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>196</v>
@@ -15918,7 +15900,7 @@
         <v>92</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>412</v>
+        <v>71</v>
       </c>
       <c r="C342" s="2" t="str">
         <f t="shared" si="5"/>
@@ -15928,7 +15910,7 @@
         <v>179</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F342" s="2" t="s">
         <v>190</v>
@@ -15958,10 +15940,10 @@
         <v>188</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G343" s="2" t="s">
         <v>29</v>
@@ -16022,7 +16004,7 @@
         <v>188</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>196</v>
@@ -16056,7 +16038,7 @@
         <v>179</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F346" s="2" t="s">
         <v>207</v>
@@ -16120,10 +16102,10 @@
         <v>179</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G348" s="2" t="s">
         <v>54</v>
@@ -16148,13 +16130,13 @@
         <v>179</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>196</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H349" s="2" t="s">
         <v>182</v>
@@ -16230,7 +16212,7 @@
         <v>96</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C352" s="2" t="str">
         <f t="shared" si="5"/>
@@ -16240,7 +16222,7 @@
         <v>192</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F352" s="2" t="s">
         <v>187</v>
@@ -16270,7 +16252,7 @@
         <v>192</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F353" s="2" t="s">
         <v>187</v>
@@ -16300,7 +16282,7 @@
         <v>192</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F354" s="2" t="s">
         <v>187</v>
@@ -16322,7 +16304,7 @@
         <v>96</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C355" s="2" t="str">
         <f t="shared" si="5"/>
@@ -16332,13 +16314,13 @@
         <v>179</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F355" s="2" t="s">
         <v>244</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H355" s="2" t="s">
         <v>244</v>
@@ -16362,7 +16344,7 @@
         <v>188</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F356" s="2" t="s">
         <v>200</v>
@@ -16392,7 +16374,7 @@
         <v>179</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F357" s="2" t="s">
         <v>196</v>
@@ -16426,7 +16408,7 @@
         <v>188</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F358" s="2" t="s">
         <v>244</v>
@@ -16495,7 +16477,7 @@
         <v>289</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G360" s="2" t="s">
         <v>10</v>
@@ -16522,10 +16504,10 @@
         <v>192</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G361" s="2" t="s">
         <v>50</v>
@@ -16576,7 +16558,7 @@
         <v>99</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>425</v>
+        <v>339</v>
       </c>
       <c r="C363" s="2" t="str">
         <f t="shared" si="5"/>
@@ -16652,7 +16634,7 @@
         <v>179</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="F365" s="2" t="s">
         <v>270</v>
@@ -16688,7 +16670,7 @@
         <v>192</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F366" s="2" t="s">
         <v>196</v>
@@ -16745,7 +16727,7 @@
         <v>179</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F368" s="2" t="s">
         <v>196</v>
@@ -16767,7 +16749,7 @@
         <v>101</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C369" s="2" t="str">
         <f t="shared" si="5"/>
@@ -16777,10 +16759,10 @@
         <v>179</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G369" s="2" t="s">
         <v>27</v>
@@ -16841,7 +16823,7 @@
         <v>188</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F371" s="2" t="s">
         <v>196</v>
@@ -16856,7 +16838,7 @@
         <v>2019</v>
       </c>
       <c r="J371" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="K371" s="2" t="s">
         <v>182</v>
@@ -16867,7 +16849,7 @@
         <v>101</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C372" s="2" t="str">
         <f t="shared" si="5"/>
@@ -16877,7 +16859,7 @@
         <v>192</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="F372" s="2" t="s">
         <v>196</v>
@@ -16899,7 +16881,7 @@
         <v>101</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C373" s="2" t="str">
         <f t="shared" si="5"/>
@@ -16911,7 +16893,7 @@
       <c r="E373" s="2"/>
       <c r="F373" s="2"/>
       <c r="G373" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H373" s="2" t="s">
         <v>196</v>
@@ -16939,7 +16921,7 @@
         <v>192</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F374" s="2" t="s">
         <v>241</v>
@@ -17138,7 +17120,7 @@
         <v>2015</v>
       </c>
       <c r="J380" s="2" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="K380" s="2" t="s">
         <v>292</v>
@@ -17159,7 +17141,7 @@
         <v>179</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F381" s="2" t="s">
         <v>235</v>
@@ -17189,7 +17171,7 @@
         <v>188</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>196</v>
@@ -17383,7 +17365,7 @@
         <v>192</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="F388" s="2" t="s">
         <v>196</v>
@@ -17462,7 +17444,7 @@
         <v>2014</v>
       </c>
       <c r="J390" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="K390" s="2" t="s">
         <v>182</v>
@@ -17496,7 +17478,7 @@
         <v>2011</v>
       </c>
       <c r="J391" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="K391" s="2" t="s">
         <v>292</v>
@@ -17537,7 +17519,7 @@
         <v>109</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C393" s="2" t="str">
         <f t="shared" si="6"/>
@@ -17575,7 +17557,7 @@
         <v>179</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>196</v>
@@ -17605,10 +17587,10 @@
         <v>179</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F395" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G395" s="2" t="s">
         <v>55</v>
@@ -17667,13 +17649,13 @@
         <v>179</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F397" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H397" s="2" t="s">
         <v>182</v>
@@ -17697,10 +17679,10 @@
         <v>192</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F398" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G398" s="2" t="s">
         <v>110</v>
@@ -17727,10 +17709,10 @@
         <v>192</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F399" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G399" s="2" t="s">
         <v>56</v>
@@ -17749,7 +17731,7 @@
         <v>110</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C400" s="2" t="str">
         <f t="shared" si="6"/>
@@ -17915,7 +17897,7 @@
         <v>192</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F405" s="2" t="s">
         <v>196</v>
@@ -17945,7 +17927,7 @@
         <v>192</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F406" s="2" t="s">
         <v>200</v>
@@ -17967,7 +17949,7 @@
         <v>113</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>444</v>
+        <v>100</v>
       </c>
       <c r="C407" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18155,7 +18137,7 @@
         <v>115</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C413" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18165,7 +18147,7 @@
         <v>179</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="F413" s="2" t="s">
         <v>238</v>
@@ -18187,7 +18169,7 @@
         <v>115</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C414" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18233,7 +18215,7 @@
         <v>179</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F415" s="2" t="s">
         <v>196</v>
@@ -18263,7 +18245,7 @@
         <v>179</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F416" s="2" t="s">
         <v>190</v>
@@ -18293,7 +18275,7 @@
         <v>179</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F417" s="2" t="s">
         <v>190</v>
@@ -18361,10 +18343,10 @@
         <v>182</v>
       </c>
       <c r="G419" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I419" s="2">
         <v>2016</v>
@@ -18385,7 +18367,7 @@
         <v>179</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>196</v>
@@ -18415,7 +18397,7 @@
         <v>188</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F421" s="2" t="s">
         <v>196</v>
@@ -18430,7 +18412,7 @@
         <v>2017</v>
       </c>
       <c r="J421" s="2" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="K421" s="2" t="s">
         <v>292</v>
@@ -18441,7 +18423,7 @@
         <v>117</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="C422" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18451,7 +18433,7 @@
         <v>188</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="F422" s="2" t="s">
         <v>196</v>
@@ -18507,7 +18489,7 @@
         <v>118</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C424" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18517,7 +18499,7 @@
         <v>179</v>
       </c>
       <c r="E424" s="2" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="F424" s="2" t="s">
         <v>207</v>
@@ -18569,7 +18551,7 @@
         <v>119</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C426" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18601,7 +18583,7 @@
         <v>119</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C427" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18611,7 +18593,7 @@
         <v>188</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="F427" s="2" t="s">
         <v>209</v>
@@ -18626,7 +18608,7 @@
         <v>2014</v>
       </c>
       <c r="J427" s="2" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="K427" s="2" t="s">
         <v>182</v>
@@ -18860,7 +18842,7 @@
         <v>179</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="F435" s="2" t="s">
         <v>235</v>
@@ -18890,7 +18872,7 @@
         <v>188</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F436" s="2" t="s">
         <v>196</v>
@@ -18912,7 +18894,7 @@
         <v>122</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C437" s="2" t="str">
         <f t="shared" si="6"/>
@@ -18986,10 +18968,10 @@
         <v>192</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="F439" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G439" s="2" t="s">
         <v>11</v>
@@ -19016,10 +18998,10 @@
         <v>192</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="F440" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G440" s="2" t="s">
         <v>158</v>
@@ -19050,7 +19032,7 @@
         <v>188</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="F441" s="2" t="s">
         <v>270</v>
@@ -19080,7 +19062,7 @@
         <v>179</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="F442" s="2" t="s">
         <v>196</v>
@@ -19113,7 +19095,7 @@
         <v>289</v>
       </c>
       <c r="F443" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G443" s="2" t="s">
         <v>5</v>
@@ -19144,10 +19126,10 @@
         <v>179</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F444" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G444" s="2" t="s">
         <v>46</v>
@@ -19208,10 +19190,10 @@
         <v>179</v>
       </c>
       <c r="E446" s="4" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F446" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="G446" s="2" t="s">
         <v>27</v>
@@ -19268,7 +19250,7 @@
         <v>179</v>
       </c>
       <c r="E448" s="4" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="F448" s="2" t="s">
         <v>196</v>
@@ -19313,7 +19295,7 @@
         <v>2018</v>
       </c>
       <c r="J449" s="2" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="K449" s="2" t="s">
         <v>292</v>
@@ -19324,7 +19306,7 @@
         <v>126</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="C450" s="2" t="str">
         <f t="shared" si="6"/>
@@ -19334,7 +19316,7 @@
         <v>192</v>
       </c>
       <c r="E450" s="4" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F450" s="2" t="s">
         <v>196</v>
@@ -19366,7 +19348,7 @@
         <v>179</v>
       </c>
       <c r="E451" s="4" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F451" s="2" t="s">
         <v>263</v>
@@ -19396,7 +19378,7 @@
         <v>179</v>
       </c>
       <c r="E452" s="4" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="F452" s="2" t="s">
         <v>196</v>
@@ -19426,7 +19408,7 @@
         <v>179</v>
       </c>
       <c r="E453" s="4" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="F453" s="2" t="s">
         <v>187</v>
@@ -19458,10 +19440,10 @@
         <v>179</v>
       </c>
       <c r="E454" s="4" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="F454" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G454" s="2" t="s">
         <v>100</v>
@@ -19488,7 +19470,7 @@
         <v>179</v>
       </c>
       <c r="E455" s="4" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="F455" s="2" t="s">
         <v>207</v>
@@ -19548,7 +19530,7 @@
         <v>192</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F457" s="2" t="s">
         <v>182</v>
@@ -19570,7 +19552,7 @@
         <v>130</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="C458" s="2" t="str">
         <f t="shared" si="7"/>
@@ -19621,7 +19603,7 @@
         <v>131</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C460" s="2" t="str">
         <f t="shared" si="7"/>
@@ -19631,10 +19613,10 @@
         <v>179</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="F460" s="2" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="G460" s="2" t="s">
         <v>50</v>
@@ -19717,7 +19699,7 @@
         <v>179</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="F463" s="2" t="s">
         <v>207</v>
@@ -19899,13 +19881,13 @@
         <v>179</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="F469" s="2" t="s">
         <v>251</v>
       </c>
       <c r="G469" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="H469" s="2" t="s">
         <v>251</v>
@@ -19929,7 +19911,7 @@
         <v>192</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="F470" s="2" t="s">
         <v>190</v>
@@ -19951,7 +19933,7 @@
         <v>133</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C471" s="2" t="str">
         <f t="shared" si="7"/>
@@ -19993,13 +19975,13 @@
         <v>179</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F472" s="2" t="s">
         <v>196</v>
       </c>
       <c r="G472" s="2" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="H472" s="2" t="s">
         <v>196</v>
@@ -20111,7 +20093,7 @@
         <v>179</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F476" s="2" t="s">
         <v>196</v>
@@ -20145,7 +20127,7 @@
         <v>192</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F477" s="2" t="s">
         <v>182</v>
@@ -20175,7 +20157,7 @@
         <v>188</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="F478" s="2" t="s">
         <v>209</v>
@@ -20209,7 +20191,7 @@
         <v>188</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F479" s="2" t="s">
         <v>209</v>
@@ -20235,7 +20217,7 @@
         <v>136</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="C480" s="2" t="str">
         <f t="shared" si="7"/>
@@ -20275,7 +20257,7 @@
         <v>179</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F481" s="2" t="s">
         <v>270</v>
@@ -20309,7 +20291,7 @@
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="H482" s="2" t="s">
         <v>235</v>
@@ -20331,10 +20313,10 @@
         <v>179</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="F483" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="G483" s="2" t="s">
         <v>10</v>
@@ -20389,7 +20371,7 @@
         <v>179</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="F485" s="2" t="s">
         <v>196</v>
@@ -20419,7 +20401,7 @@
         <v>188</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F486" s="2" t="s">
         <v>241</v>
@@ -20449,7 +20431,7 @@
         <v>179</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="F487" s="2" t="s">
         <v>207</v>
@@ -20479,7 +20461,7 @@
         <v>188</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F488" s="2" t="s">
         <v>187</v>
@@ -20513,7 +20495,7 @@
         <v>188</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="F489" s="2" t="s">
         <v>187</v>
@@ -20579,7 +20561,7 @@
         <v>192</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="F491" s="2" t="s">
         <v>200</v>
@@ -20609,7 +20591,7 @@
         <v>192</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="F492" s="2" t="s">
         <v>182</v>
@@ -20642,7 +20624,7 @@
         <v>289</v>
       </c>
       <c r="F493" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G493" s="2" t="s">
         <v>10</v>
@@ -20669,10 +20651,10 @@
         <v>192</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="F494" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="G494" s="2" t="s">
         <v>84</v>
@@ -20789,7 +20771,7 @@
         <v>143</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="C498" s="2" t="str">
         <f t="shared" si="7"/>
@@ -20814,10 +20796,10 @@
         <v>2014</v>
       </c>
       <c r="J498" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="K498" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="499" spans="1:11" ht="22.5" customHeight="1">
@@ -20863,7 +20845,7 @@
         <v>188</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F500" s="2" t="s">
         <v>209</v>
@@ -20891,10 +20873,10 @@
         <v>192</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F501" s="2" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="G501" s="2" t="s">
         <v>95</v>
@@ -20980,10 +20962,10 @@
         <v>289</v>
       </c>
       <c r="F504" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H504" s="2" t="s">
         <v>182</v>
@@ -21007,7 +20989,7 @@
         <v>179</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F505" s="2" t="s">
         <v>182</v>
@@ -21035,10 +21017,10 @@
         <v>188</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F506" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G506" s="2" t="s">
         <v>56</v>
@@ -21161,7 +21143,7 @@
         <v>188</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="F510" s="2" t="s">
         <v>196</v>
@@ -21187,7 +21169,7 @@
         <v>146</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C511" s="2" t="str">
         <f t="shared" si="7"/>
@@ -21231,7 +21213,7 @@
         <v>179</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="F512" s="2" t="s">
         <v>181</v>
@@ -21353,7 +21335,7 @@
         <v>179</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F516" s="2" t="s">
         <v>190</v>
@@ -21383,7 +21365,7 @@
         <v>192</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F517" s="2" t="s">
         <v>182</v>
@@ -21437,10 +21419,10 @@
         <v>188</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F519" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G519" s="2" t="s">
         <v>94</v>
@@ -21452,7 +21434,7 @@
         <v>2021</v>
       </c>
       <c r="J519" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="K519" s="2" t="s">
         <v>182</v>
@@ -21501,7 +21483,7 @@
         <v>179</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F521" s="2" t="s">
         <v>270</v>
@@ -21719,10 +21701,10 @@
         <v>192</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="F528" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G528" s="2" t="s">
         <v>103</v>
@@ -21749,10 +21731,10 @@
         <v>192</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F529" s="2" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="G529" s="2" t="s">
         <v>15</v>
@@ -21859,7 +21841,7 @@
         <v>179</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>412</v>
+        <v>71</v>
       </c>
       <c r="F533" s="2" t="s">
         <v>182</v>
@@ -21983,7 +21965,7 @@
         <v>188</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F537" s="2" t="s">
         <v>241</v>
@@ -22042,7 +22024,7 @@
         <v>179</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="F539" s="2" t="s">
         <v>207</v>
@@ -22072,7 +22054,7 @@
         <v>188</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="F540" s="2" t="s">
         <v>270</v>
@@ -22098,7 +22080,7 @@
         <v>159</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="C541" s="2" t="str">
         <f t="shared" si="8"/>
@@ -22108,13 +22090,13 @@
         <v>179</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="F541" s="2" t="s">
         <v>200</v>
       </c>
       <c r="G541" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="H541" s="2" t="s">
         <v>248</v>
@@ -22153,7 +22135,7 @@
         <v>192</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="F543" s="2" t="s">
         <v>235</v>
@@ -22175,7 +22157,7 @@
         <v>160</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C544" s="2" t="str">
         <f t="shared" si="8"/>
@@ -22185,10 +22167,10 @@
         <v>192</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="F544" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G544" s="2" t="s">
         <v>124</v>
@@ -22198,7 +22180,7 @@
       </c>
       <c r="I544" s="2"/>
       <c r="J544" s="2" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="K544" s="2" t="s">
         <v>182</v>
@@ -22217,10 +22199,10 @@
         <v>179</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F545" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G545" s="2" t="s">
         <v>27</v>
@@ -22295,10 +22277,10 @@
         <v>179</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="F548" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G548" s="2" t="s">
         <v>153</v>
@@ -22315,7 +22297,7 @@
         <v>163</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C549" s="2" t="str">
         <f t="shared" si="8"/>
@@ -22325,10 +22307,10 @@
         <v>179</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="F549" s="2" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G549" s="2" t="s">
         <v>135</v>
@@ -22359,10 +22341,10 @@
         <v>179</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F550" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G550" s="2" t="s">
         <v>50</v>
@@ -22423,7 +22405,7 @@
         <v>192</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="F552" s="2" t="s">
         <v>187</v>
